--- a/docs/data/jp/xlsx/7241.xlsx
+++ b/docs/data/jp/xlsx/7241.xlsx
@@ -8562,7 +8562,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Restructuring Loss EL</t>
+          <t>사업재편 손실</t>
         </is>
       </c>
       <c r="E122" s="20" t="n">
@@ -11710,7 +11710,7 @@
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>Reversal Of Impairment Losses Ope CF</t>
+          <t>손상차손 환입이익</t>
         </is>
       </c>
       <c r="E186" s="20" t="n">
@@ -11920,7 +11920,7 @@
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Reserve For Demolition And Removal Ope CF</t>
+          <t>해체철거 충당금 증감액</t>
         </is>
       </c>
       <c r="E192" s="20" t="n">
@@ -12056,7 +12056,7 @@
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>Loss On Abandonment Of Property Plant And Equipment Ope CF</t>
+          <t>유형자산 폐기손실</t>
         </is>
       </c>
       <c r="E196" s="20" t="n">
@@ -12174,7 +12174,7 @@
     <row r="200">
       <c r="A200" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Liquidity Of Affiliated Company Ope CF</t>
+          <t>관계회사 주식 청산손익</t>
         </is>
       </c>
       <c r="Q200" s="20" t="n">
@@ -12309,7 +12309,7 @@
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>Loss On Business Restructuring Ope CF</t>
+          <t>사업재편 손실</t>
         </is>
       </c>
       <c r="E206" s="20" t="n">
@@ -12795,7 +12795,7 @@
     <row r="218">
       <c r="A218" s="18" t="inlineStr">
         <is>
-          <t>Business Structure Improvement Expenses Paid Ope CF</t>
+          <t>사업구조개선 비용 지급액</t>
         </is>
       </c>
       <c r="E218" s="20" t="n">
@@ -12820,7 +12820,7 @@
     <row r="219">
       <c r="A219" s="18" t="inlineStr">
         <is>
-          <t>Payments For Loss On Business Restructuring Ope CF</t>
+          <t>사업재편 손실 지급액</t>
         </is>
       </c>
       <c r="E219" s="20" t="n">
@@ -13182,7 +13182,7 @@
     <row r="230">
       <c r="A230" s="18" t="inlineStr">
         <is>
-          <t>Payment For Sales Of Investment In Affiliates Resulting In Change In Scope Of Consolidation Inv CF</t>
+          <t>연결범위 변경 관계회사 출자금 매각 지출</t>
         </is>
       </c>
       <c r="P230" s="20" t="n">
@@ -13204,7 +13204,7 @@
     <row r="231">
       <c r="A231" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Cash And Cash Equivalents Resulting From Exclusion Of Subsidiaries From Consolidation CF</t>
+          <t>연결 제외에 따른 현금성자산 증감액</t>
         </is>
       </c>
       <c r="I231" s="20" t="n">
@@ -13696,7 +13696,7 @@
     <row r="246">
       <c r="A246" s="18" t="inlineStr">
         <is>
-          <t>Payments From Changes In Investments In Capital Of Subsidiaries And Associates That Do Not Result In Change In Scope Of Consolidation Fin CF</t>
+          <t>연결범위 변경 없는 관계회사 출자금 취득 지출</t>
         </is>
       </c>
       <c r="S246" s="20" t="n">
@@ -13896,7 +13896,7 @@
     <row r="251">
       <c r="A251" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Cash And Cash Equivalents Resulting From AChange In Closing Dates Of Consolidated Subsidiaries CCE</t>
+          <t>연결자회사 결산기 변경에 따른 현금성자산 증감액</t>
         </is>
       </c>
       <c r="E251" s="20" t="n">
@@ -18454,7 +18454,7 @@
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>Provision For Environmental Measures NCL</t>
+          <t>환경대책 충당금</t>
         </is>
       </c>
       <c r="C124" s="20" t="n">
@@ -18485,7 +18485,7 @@
     <row r="125">
       <c r="A125" s="18" t="inlineStr">
         <is>
-          <t>Provision For Decommissioning And Removal NCL</t>
+          <t>해체철거 충당금</t>
         </is>
       </c>
       <c r="C125" s="20" t="n">
